--- a/Resultado.xlsx
+++ b/Resultado.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD4D361C20488D9ACD6DCCA62DD95A705ADEDD9A" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6CC94ADE-84FC-4E99-BEEB-5708BA5FF0FC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -18,15 +19,269 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="81">
+  <si>
+    <t>1)</t>
+  </si>
+  <si>
+    <t>1.3724790000014764</t>
+  </si>
+  <si>
+    <t>1.3001679999997577</t>
+  </si>
+  <si>
+    <t>1.3037521999995079</t>
+  </si>
+  <si>
+    <t>1.2985508000001573</t>
+  </si>
+  <si>
+    <t>1.299856900001032</t>
+  </si>
+  <si>
+    <t>3)</t>
+  </si>
+  <si>
+    <t>Número de processos</t>
+  </si>
+  <si>
+    <t>Tempo de execução</t>
+  </si>
+  <si>
+    <t>Speedup</t>
+  </si>
+  <si>
+    <t>Eficiência</t>
+  </si>
+  <si>
+    <t>1.311826299999666</t>
+  </si>
+  <si>
+    <t>0.7694790000005014</t>
+  </si>
+  <si>
+    <t>1.6715051352927912</t>
+  </si>
+  <si>
+    <t>0.8357525676463956</t>
+  </si>
+  <si>
+    <t>0.4581417999997939</t>
+  </si>
+  <si>
+    <t>2.8074017694988287</t>
+  </si>
+  <si>
+    <t>0.7018504423747072</t>
+  </si>
+  <si>
+    <t>0.3657891999991989</t>
+  </si>
+  <si>
+    <t>3.516200314289259</t>
+  </si>
+  <si>
+    <t>0.4395250392861574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4) </t>
+  </si>
+  <si>
+    <t>b) A eficiência do processamento paralelo foi diminuindo conforme aumentava o número de processos, com dois processos a eficiência por processo foi de aproximadamente 85%, com 4 processos foi de aproximadamente 70% e com oito processos foi de aproximadamente 44%</t>
+  </si>
+  <si>
+    <t>a) Não, o speedup ficou um pouco abaixo do número de processos, e essa diferença foi aumentando quanto mais processos foram sendo adicionados, indicando que o ganho não foi proporcional ao aumento dos processos</t>
+  </si>
+  <si>
+    <t>c) O tempo de execução também diminuiu com o aumento do número de processos, porém sofreu do mesmo problema que o speedup, o ganho de desempenho não foi proporcional ao aumento do número de processos</t>
+  </si>
+  <si>
+    <t>d) Sim. O ganho de desempenho para cada aumento de processos foi diminuindo conforme o número de processos aumentava, o ganho de 1 para dois foi muito maior do que o ganho de 4 para 8, por exemplo</t>
+  </si>
+  <si>
+    <t>e) Quanto mais processos você possui, mais recursos a máquina irá gastar para conseguir fazer todos eles trabalharem de maneira conjunta, desde a criação, até a divisão das tarefas, o gerenciamento da execução dessas tarefas e por final o retorno dos resultados para o processo principal, isso tudo gera overhead</t>
+  </si>
+  <si>
+    <t>5)</t>
+  </si>
+  <si>
+    <t>0.26032110000051034</t>
+  </si>
+  <si>
+    <t>1.059138940606833</t>
+  </si>
+  <si>
+    <t>0.5295694703034165</t>
+  </si>
+  <si>
+    <t>0.20794260000002396</t>
+  </si>
+  <si>
+    <t>0.2457856000000902</t>
+  </si>
+  <si>
+    <t>1.2518892232783487</t>
+  </si>
+  <si>
+    <t>0.3129723058195872</t>
+  </si>
+  <si>
+    <t>0.20899649999955727</t>
+  </si>
+  <si>
+    <t>1.2455763613317055</t>
+  </si>
+  <si>
+    <t>0.15569704516646318</t>
+  </si>
+  <si>
+    <t>Lista (1, 21)</t>
+  </si>
+  <si>
+    <t>Lista (1, 101)</t>
+  </si>
+  <si>
+    <t>1.3337659000007989</t>
+  </si>
+  <si>
+    <t>0.7882573000006232</t>
+  </si>
+  <si>
+    <t>1.6920438288357678</t>
+  </si>
+  <si>
+    <t>0.8460219144178839</t>
+  </si>
+  <si>
+    <t>0.4547043999991729</t>
+  </si>
+  <si>
+    <t>2.9332592779027977</t>
+  </si>
+  <si>
+    <t>0.7333148194756994</t>
+  </si>
+  <si>
+    <t>0.35873630000060075</t>
+  </si>
+  <si>
+    <t>3.717956337283306</t>
+  </si>
+  <si>
+    <t>0.4647445421604133</t>
+  </si>
+  <si>
+    <t>Lista (1, 501)</t>
+  </si>
+  <si>
+    <t>6.422736700000314</t>
+  </si>
+  <si>
+    <t>3.708863300000303</t>
+  </si>
+  <si>
+    <t>1.7317264564589883</t>
+  </si>
+  <si>
+    <t>0.8658632282294941</t>
+  </si>
+  <si>
+    <t>1.909522099998867</t>
+  </si>
+  <si>
+    <t>3.3635309588740165</t>
+  </si>
+  <si>
+    <t>0.8408827397185041</t>
+  </si>
+  <si>
+    <t>1.251475200000641</t>
+  </si>
+  <si>
+    <t>5.132132622362013</t>
+  </si>
+  <si>
+    <t>0.6415165777952516</t>
+  </si>
+  <si>
+    <t>a) Quanto maior a quantidade de tarefas, melhor tende a ser o aproveitamento dos processos, pois existe mais trabalho para ser distribuído entre eles</t>
+  </si>
+  <si>
+    <t>b) Sim. Tarefas muito pequenas podem prejudicar o desempenho, o tempo e os recursos gastos para distribuir e gerenciar as tarefas podem ser significativos em comparação ao tempo necessário para executar o próprio processamento</t>
+  </si>
+  <si>
+    <t>c) O ganho do desempenho diminui, uma parte significativa do tempo passa a ser utilizada para distribuir e gerenciar as tarefas nos processos novos, o overhead pode compensar parte do ganho que seria obtido com o paralelismo</t>
+  </si>
+  <si>
+    <t>d) Esses resultados mostram que a granulidade afeta o aproveitamento do uso de processamento paralelo. Nos testes com mais tarefas, existe mais trabalho a ser distribuído entre os processos, o que pode melhor o aproveitamento, mas quando as tarefas são muito pequenas, o overhead da distribuição e gerencimaneto dessas tarefas pode reduzir o ganho de desempenho</t>
+  </si>
+  <si>
+    <t>6)</t>
+  </si>
+  <si>
+    <t>Lista (1,101) com processos pesados</t>
+  </si>
+  <si>
+    <t>1.8609351000013703</t>
+  </si>
+  <si>
+    <t>1.060733700000128</t>
+  </si>
+  <si>
+    <t>1.7543848187355089</t>
+  </si>
+  <si>
+    <t>0.8771924093677544</t>
+  </si>
+  <si>
+    <t>0.6691133000003902</t>
+  </si>
+  <si>
+    <t>2.7811958004724837</t>
+  </si>
+  <si>
+    <t>0.6952989501181209</t>
+  </si>
+  <si>
+    <t>0.5422465999999986</t>
+  </si>
+  <si>
+    <t>3.4318981437622202</t>
+  </si>
+  <si>
+    <t>0.42898726797027753</t>
+  </si>
+  <si>
+    <t>a) Pode ser que, devido à distribuição das tarefas mais pesadas, alguns processos recebam mais trabalho e acabem demorando mais para finalizar do que os outros</t>
+  </si>
+  <si>
+    <t>b) O balanceamento não foi totalmente adequado porque alguns processos podem acabar recebendo trabalhos mais pesados, enquanto outros processos podem terminar suas tarefas antes e ficar ociosos</t>
+  </si>
+  <si>
+    <t>c) Sim, se algum processo não receber essas tarefas pesadas ele pode acabar antes dos outros e ficar ocioso esperando os outros terminarem as tarefas</t>
+  </si>
+  <si>
+    <t>d) Sim, dividir em tarefas menores poderia melhor a distribuição, porém isso também daria mais trabalho para gerenciar todos as tarefas, o que poderia atrapalhar no desempenho</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF273540"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +304,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +594,497 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="4" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>4</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E14" s="4"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3">
+        <v>4</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="4">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C31" s="3">
+        <v>2</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C32" s="3">
+        <v>4</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C33" s="3">
+        <v>8</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C37" s="3">
+        <v>2</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C38" s="3">
+        <v>4</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C39" s="3">
+        <v>8</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C49" s="3">
+        <v>1</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C50" s="3">
+        <v>2</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C51" s="3">
+        <v>4</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C52" s="3">
+        <v>8</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="B2:B5 C9 D10:D12" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Resultado.xlsx
+++ b/Resultado.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD4D361C20488D9ACD6DCCA62DD95A705ADEDD9A" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6CC94ADE-84FC-4E99-BEEB-5708BA5FF0FC}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_AD4D361C20488D9ACD6DCCA62DD95A705ADEDD9A" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{DBEA20D6-7158-412D-B483-E5D63003F317}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="82">
   <si>
     <t>1)</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>d) Sim, dividir em tarefas menores poderia melhor a distribuição, porém isso também daria mais trabalho para gerenciar todos as tarefas, o que poderia atrapalhar no desempenho</t>
+  </si>
+  <si>
+    <t>Análise final: Os resultados confirmam que adicionar mais processos não produz necessariamente um ganho proporcional de desempenho. Mesmo tendo um ganho no speedup conforme o aumento de processos, ele ficou abaixo do ideal, que seria ter um valor igual ao número de processos. Isso também significa que a eficiência diminui conforme mais processos foram utilizados. Isso pode ocorrer devido ao overhead causado pela criação e o gerenciamento dos processos, distribuição das tarefas e depois a coleta dos resultados para o processo principal. A granularidade também influencia no desempenho, tarefas muito pequenas podem gerar um overhead significativo, enquanto tarefas maiores podem dificultar o balanceamento dessa carga entre os processos, alguns podem receber mais trabalhos do que outros e permanecer ocupados enquantos os outros ficam ociosos. E segundo a Lei de Amdahl que diz que nem todo programa pode ser paralelizado limita o speedup máximo, fazendo com que o aumento do número de processos não resulte em um ganho proporcional de desempenho</t>
   </si>
 </sst>
 </file>
@@ -595,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.85546875" customWidth="1"/>
@@ -1080,6 +1083,11 @@
         <v>80</v>
       </c>
     </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
